--- a/analysis/tables/pythia-160m.xlsx
+++ b/analysis/tables/pythia-160m.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4871200924961712</v>
+        <v>0.3539739338805509</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1066703595919612</v>
+        <v>-0.05471088305903625</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.487x - 0.107</t>
+          <t>y = 0.354x - 0.055</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.5218989987117629</v>
+        <v>0.5218989987117625</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0696855860505106</v>
+        <v>0.06968558605051059</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2189816458716485</v>
+        <v>0.1545618979885071</v>
       </c>
       <c r="J3" t="n">
-        <v>0.38044973290421</v>
+        <v>0.2992630508215146</v>
       </c>
       <c r="K3" t="n">
         <v>0.07069818022188841</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.866546096382967</v>
+        <v>0.3533884572598817</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05638404044587862</v>
+        <v>-0.05118674385996176</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 1.867x + 0.056</t>
+          <t>y = 0.353x - 0.051</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.6113561207258259</v>
+        <v>0.5259638817785133</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06795561670435361</v>
+        <v>0.06960697718245326</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03020768710461575</v>
+        <v>0.144845545485146</v>
       </c>
       <c r="J4" t="n">
-        <v>1.922930136828846</v>
+        <v>0.30220171339992</v>
       </c>
       <c r="K4" t="n">
         <v>0.07069818022188841</v>
